--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260609.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.72%</t>
+          <t>12.82%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.23%</t>
+          <t>10.76%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>6.94%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>5.07%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -880,46 +880,46 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,334,000</t>
+          <t>2,827,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>14,334,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -990,46 +990,46 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>14,856,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19,861,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>19,861,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1100,29 +1100,29 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,770,170,471</t>
+          <t>20,131,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1166,29 +1166,29 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>20,131,000</t>
+          <t>1,678,954,055</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>2,697,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,697,000</t>
+          <t>1,868,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>857,064,462</t>
+          <t>908,072,462</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-385,769,997</t>
+          <t>-294,553,581</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.22%</t>
         </is>
       </c>
     </row>
